--- a/output/pdf_financials_xlsx/LUXR.xlsx
+++ b/output/pdf_financials_xlsx/LUXR.xlsx
@@ -1984,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.007309</v>
       </c>
     </row>
     <row r="119">
@@ -2916,7 +2916,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LUXR.xlsx
+++ b/output/pdf_financials_xlsx/LUXR.xlsx
@@ -556,7 +556,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.035275</v>
+        <v>0.077975</v>
       </c>
     </row>
     <row r="11">
@@ -569,7 +569,7 @@
         <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.035275</v>
+        <v>-0.077975</v>
       </c>
     </row>
     <row r="12">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.22802</v>
       </c>
     </row>
     <row r="35">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>2.769231</v>
+        <v>2.997251</v>
       </c>
     </row>
     <row r="37">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.229395</v>
+        <v>0.001375</v>
       </c>
     </row>
     <row r="49">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">

--- a/output/pdf_financials_xlsx/LUXR.xlsx
+++ b/output/pdf_financials_xlsx/LUXR.xlsx
@@ -3002,7 +3002,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>1e-06</v>
       </c>
